--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78047535</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78047529</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78047518</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78047520</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119048437</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129728749</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106979909</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107956511</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106979947</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1775,6 +1825,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62805101</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1877,6 +1932,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62805107</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1979,6 +2039,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62805103</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62805102</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2183,6 +2253,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62805104</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2303,6 +2378,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17205203</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2421,6 +2501,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/9612</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2547,6 +2632,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67277682</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2666,6 +2756,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133676150</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2785,6 +2880,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133676157</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2902,6 +3002,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115464146</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3018,6 +3123,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118256343</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3134,6 +3244,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118256359</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3250,6 +3365,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118256345</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3357,6 +3477,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16802844</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3464,6 +3589,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16802843</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3583,6 +3713,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117969100</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3700,6 +3835,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635114</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3825,6 +3965,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134803960</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3950,6 +4095,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134804509</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4075,6 +4225,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134810115</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4191,6 +4346,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134804582</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4307,6 +4467,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134806613</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4412,6 +4577,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490287</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4517,6 +4687,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490290</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4622,6 +4797,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490318</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4727,6 +4907,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490374</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4832,6 +5017,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490311</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4937,6 +5127,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490404</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5042,6 +5237,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490422</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5147,6 +5347,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490286</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5254,6 +5459,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490417</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5361,6 +5571,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490336</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5468,6 +5683,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490321</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5575,6 +5795,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104734918</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5682,6 +5907,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104734973</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5789,6 +6019,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104734987</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5896,6 +6131,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490370</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6002,6 +6242,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490371</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6108,6 +6353,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120490271</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6231,6 +6481,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133676469</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6350,6 +6605,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134223604</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6469,6 +6729,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134174906</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6580,6 +6845,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62686291</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6677,6 +6947,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451223</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6774,6 +7049,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78430052</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6871,6 +7151,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54014137</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6968,6 +7253,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451486</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7070,6 +7360,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563834</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7167,6 +7462,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451487</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7264,6 +7564,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451488</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7368,6 +7673,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55322405</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7483,6 +7793,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98101330</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7580,6 +7895,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451507</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7677,6 +7997,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451509</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7774,6 +8099,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451483</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7871,6 +8201,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451531</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7968,6 +8303,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451532</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8073,6 +8413,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119730876</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8175,6 +8520,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563835</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8294,6 +8644,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79351146</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8413,6 +8768,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79351057</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8522,6 +8882,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90856737</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8626,8 +8991,88 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55322391</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ74"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2640,60 +2640,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133676150</v>
+        <v>135859839</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>58141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gubbhult, Nrk</t>
+          <t>Lissjön, Lissjön, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515778</v>
+        <v>517700</v>
       </c>
       <c r="R19" t="n">
-        <v>6537705</v>
+        <v>6538510</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,22 +2714,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,44 +2744,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Tomas Carlberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133676150</t>
+          <t>https://artportalen.se/Sighting/135859839</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133676157</v>
+        <v>133676150</v>
       </c>
       <c r="B20" t="n">
-        <v>58519</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2882,63 +2879,66 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133676157</t>
+          <t>https://artportalen.se/Sighting/133676150</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115464146</v>
+        <v>133676157</v>
       </c>
       <c r="B21" t="n">
-        <v>8444</v>
+        <v>58519</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106554</v>
+        <v>102990</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ommekärrsmossen, Nrk</t>
+          <t>Gubbhult, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521086</v>
+        <v>515778</v>
       </c>
       <c r="R21" t="n">
-        <v>6536745</v>
+        <v>6537705</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2962,22 +2962,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,34 +2986,33 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115464146</t>
+          <t>https://artportalen.se/Sighting/133676157</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118256343</v>
+        <v>115464146</v>
       </c>
       <c r="B22" t="n">
-        <v>99035</v>
+        <v>8444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3021,45 +3020,46 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Orrmossen, Nrk</t>
+          <t>Ommekärrsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521123</v>
+        <v>521086</v>
       </c>
       <c r="R22" t="n">
-        <v>6536140</v>
+        <v>6536745</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3083,22 +3083,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,13 +3125,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118256343</t>
+          <t>https://artportalen.se/Sighting/115464146</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118256359</v>
+        <v>118256343</v>
       </c>
       <c r="B23" t="n">
         <v>99035</v>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521007</v>
+        <v>521123</v>
       </c>
       <c r="R23" t="n">
-        <v>6536162</v>
+        <v>6536140</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3246,16 +3246,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118256359</t>
+          <t>https://artportalen.se/Sighting/118256343</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118256345</v>
+        <v>118256359</v>
       </c>
       <c r="B24" t="n">
-        <v>97986</v>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3263,21 +3263,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221946</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521123</v>
+        <v>521007</v>
       </c>
       <c r="R24" t="n">
-        <v>6536140</v>
+        <v>6536162</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3367,16 +3367,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118256345</t>
+          <t>https://artportalen.se/Sighting/118256359</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16802844</v>
+        <v>118256345</v>
       </c>
       <c r="B25" t="n">
-        <v>91680</v>
+        <v>97986</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3384,34 +3384,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>221946</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Orrmossen, Nrk</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521436</v>
+        <v>521123</v>
       </c>
       <c r="R25" t="n">
-        <v>6535767</v>
+        <v>6536140</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3438,17 +3446,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2014-09-22</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2014-09-22</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>medobservatör: Mats Andersson</t>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3457,38 +3470,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>marken</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16802844</t>
+          <t>https://artportalen.se/Sighting/118256345</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16802843</v>
+        <v>16802844</v>
       </c>
       <c r="B26" t="n">
-        <v>92869</v>
+        <v>91680</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3496,21 +3505,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3591,65 +3600,54 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/16802843</t>
+          <t>https://artportalen.se/Sighting/16802844</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117969100</v>
+        <v>16802843</v>
       </c>
       <c r="B27" t="n">
-        <v>91930</v>
+        <v>92869</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Böltorpa mosse, Nrk</t>
+          <t>Orrmossen, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>522571</v>
+        <v>521436</v>
       </c>
       <c r="R27" t="n">
-        <v>6535998</v>
+        <v>6535767</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3673,22 +3671,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2014-09-22</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>medobservatör: Mats Andersson</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,34 +3690,38 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>marken</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117969100</t>
+          <t>https://artportalen.se/Sighting/16802843</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120635114</v>
+        <v>117969100</v>
       </c>
       <c r="B28" t="n">
-        <v>5178</v>
+        <v>91930</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3732,43 +3729,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102204</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Böltorpa mosse, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>517596</v>
+        <v>522571</v>
       </c>
       <c r="R28" t="n">
-        <v>6536395</v>
+        <v>6535998</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3795,22 +3794,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3837,71 +3836,63 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635114</t>
+          <t>https://artportalen.se/Sighting/117969100</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134803960</v>
+        <v>120635114</v>
       </c>
       <c r="B29" t="n">
-        <v>45055</v>
+        <v>5178</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102021</v>
+        <v>102204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>friflygande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bavlinge, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519835</v>
+        <v>517596</v>
       </c>
       <c r="R29" t="n">
-        <v>6535070</v>
+        <v>6536395</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3925,22 +3916,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3956,24 +3947,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134803960</t>
+          <t>https://artportalen.se/Sighting/120635114</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134804509</v>
+        <v>134803960</v>
       </c>
       <c r="B30" t="n">
         <v>45055</v>
@@ -4028,10 +4019,10 @@
         <v>519835</v>
       </c>
       <c r="R30" t="n">
-        <v>6535071</v>
+        <v>6535070</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4086,27 +4077,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134804509</t>
+          <t>https://artportalen.se/Sighting/134803960</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134810115</v>
+        <v>134804509</v>
       </c>
       <c r="B31" t="n">
-        <v>43314</v>
+        <v>45055</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4114,21 +4105,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>201146</v>
+        <v>102021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silverblåvinge</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Polyommatus amandus</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schneider, 1792)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4227,48 +4218,57 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134810115</t>
+          <t>https://artportalen.se/Sighting/134804509</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134804582</v>
+        <v>134810115</v>
       </c>
       <c r="B32" t="n">
-        <v>108205</v>
+        <v>43314</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220083</v>
+        <v>201146</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Silverblåvinge</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polyommatus amandus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4348,13 +4348,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134804582</t>
+          <t>https://artportalen.se/Sighting/134810115</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134806613</v>
+        <v>134804582</v>
       </c>
       <c r="B33" t="n">
         <v>108205</v>
@@ -4400,10 +4400,10 @@
         <v>519835</v>
       </c>
       <c r="R33" t="n">
-        <v>6535070</v>
+        <v>6535071</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4458,72 +4458,73 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134806613</t>
+          <t>https://artportalen.se/Sighting/134804582</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120490287</v>
+        <v>134806613</v>
       </c>
       <c r="B34" t="n">
-        <v>75428</v>
+        <v>108205</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6426</v>
+        <v>220083</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Bavlinge, Nrk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518469</v>
+        <v>519835</v>
       </c>
       <c r="R34" t="n">
-        <v>6535004</v>
+        <v>6535070</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4547,12 +4548,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4568,24 +4579,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490287</t>
+          <t>https://artportalen.se/Sighting/134806613</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120490290</v>
+        <v>120490287</v>
       </c>
       <c r="B35" t="n">
         <v>75428</v>
@@ -4627,10 +4638,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518452</v>
+        <v>518469</v>
       </c>
       <c r="R35" t="n">
-        <v>6535003</v>
+        <v>6535004</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4689,13 +4700,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490290</t>
+          <t>https://artportalen.se/Sighting/120490287</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120490318</v>
+        <v>120490290</v>
       </c>
       <c r="B36" t="n">
         <v>75428</v>
@@ -4737,10 +4748,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518444</v>
+        <v>518452</v>
       </c>
       <c r="R36" t="n">
-        <v>6535002</v>
+        <v>6535003</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4799,13 +4810,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490318</t>
+          <t>https://artportalen.se/Sighting/120490290</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120490374</v>
+        <v>120490318</v>
       </c>
       <c r="B37" t="n">
         <v>75428</v>
@@ -4847,10 +4858,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518426</v>
+        <v>518444</v>
       </c>
       <c r="R37" t="n">
-        <v>6534998</v>
+        <v>6535002</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4909,38 +4920,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490374</t>
+          <t>https://artportalen.se/Sighting/120490318</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120490311</v>
+        <v>120490374</v>
       </c>
       <c r="B38" t="n">
-        <v>75300</v>
+        <v>75428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6428</v>
+        <v>6426</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4957,10 +4968,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518448</v>
+        <v>518426</v>
       </c>
       <c r="R38" t="n">
-        <v>6535004</v>
+        <v>6534998</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5019,38 +5030,38 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490311</t>
+          <t>https://artportalen.se/Sighting/120490374</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120490404</v>
+        <v>120490311</v>
       </c>
       <c r="B39" t="n">
-        <v>79946</v>
+        <v>75300</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6428</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5063,14 +5074,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Molångsbergen, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>518400</v>
+        <v>518448</v>
       </c>
       <c r="R39" t="n">
-        <v>6535136</v>
+        <v>6535004</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5129,13 +5140,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490404</t>
+          <t>https://artportalen.se/Sighting/120490311</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120490422</v>
+        <v>120490404</v>
       </c>
       <c r="B40" t="n">
         <v>79946</v>
@@ -5177,10 +5188,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518597</v>
+        <v>518400</v>
       </c>
       <c r="R40" t="n">
-        <v>6535166</v>
+        <v>6535136</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5239,38 +5250,38 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490422</t>
+          <t>https://artportalen.se/Sighting/120490404</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120490286</v>
+        <v>120490422</v>
       </c>
       <c r="B41" t="n">
-        <v>79583</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6459</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5283,14 +5294,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Molångsbergen, Nrk</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518469</v>
+        <v>518597</v>
       </c>
       <c r="R41" t="n">
-        <v>6535004</v>
+        <v>6535166</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5349,16 +5360,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490286</t>
+          <t>https://artportalen.se/Sighting/120490422</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120490417</v>
+        <v>120490286</v>
       </c>
       <c r="B42" t="n">
-        <v>4775</v>
+        <v>79583</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5366,43 +5377,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100299</v>
+        <v>6459</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Molångsbergen, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518449</v>
+        <v>518469</v>
       </c>
       <c r="R42" t="n">
-        <v>6535170</v>
+        <v>6535004</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5461,16 +5470,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490417</t>
+          <t>https://artportalen.se/Sighting/120490286</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120490336</v>
+        <v>120490417</v>
       </c>
       <c r="B43" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5478,21 +5487,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5507,14 +5516,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Molångsbergen, Nrk</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518436</v>
+        <v>518449</v>
       </c>
       <c r="R43" t="n">
-        <v>6535000</v>
+        <v>6535170</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5573,16 +5582,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490336</t>
+          <t>https://artportalen.se/Sighting/120490417</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120490321</v>
+        <v>120490336</v>
       </c>
       <c r="B44" t="n">
-        <v>5199</v>
+        <v>5179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5590,21 +5599,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5613,7 +5622,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5623,10 +5632,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518445</v>
+        <v>518436</v>
       </c>
       <c r="R44" t="n">
-        <v>6535003</v>
+        <v>6535000</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5685,16 +5694,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490321</t>
+          <t>https://artportalen.se/Sighting/120490336</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>104734918</v>
+        <v>120490321</v>
       </c>
       <c r="B45" t="n">
-        <v>8444</v>
+        <v>5199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5702,21 +5711,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5731,14 +5740,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Molångsbergen, Fåglamossen-Bavlingebäcken, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518600</v>
+        <v>518445</v>
       </c>
       <c r="R45" t="n">
-        <v>6535166</v>
+        <v>6535003</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5765,12 +5774,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5797,13 +5806,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104734918</t>
+          <t>https://artportalen.se/Sighting/120490321</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>104734973</v>
+        <v>104734918</v>
       </c>
       <c r="B46" t="n">
         <v>8444</v>
@@ -5847,10 +5856,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518493</v>
+        <v>518600</v>
       </c>
       <c r="R46" t="n">
-        <v>6535135</v>
+        <v>6535166</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5909,13 +5918,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104734973</t>
+          <t>https://artportalen.se/Sighting/104734918</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>104734987</v>
+        <v>104734973</v>
       </c>
       <c r="B47" t="n">
         <v>8444</v>
@@ -5959,10 +5968,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518564</v>
+        <v>518493</v>
       </c>
       <c r="R47" t="n">
-        <v>6535128</v>
+        <v>6535135</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6021,13 +6030,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104734987</t>
+          <t>https://artportalen.se/Sighting/104734973</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120490370</v>
+        <v>104734987</v>
       </c>
       <c r="B48" t="n">
         <v>8444</v>
@@ -6061,20 +6070,20 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Molångsfallet, Nrk</t>
+          <t>Molångsbergen, Fåglamossen-Bavlingebäcken, Nrk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518443</v>
+        <v>518564</v>
       </c>
       <c r="R48" t="n">
-        <v>6534984</v>
+        <v>6535128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6101,12 +6110,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6133,16 +6142,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490370</t>
+          <t>https://artportalen.se/Sighting/104734987</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120490371</v>
+        <v>120490370</v>
       </c>
       <c r="B49" t="n">
-        <v>99035</v>
+        <v>8444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6150,31 +6159,32 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219790</v>
+        <v>106554</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6182,10 +6192,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518426</v>
+        <v>518443</v>
       </c>
       <c r="R49" t="n">
-        <v>6534993</v>
+        <v>6534984</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6244,16 +6254,16 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490371</t>
+          <t>https://artportalen.se/Sighting/120490370</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120490271</v>
+        <v>120490371</v>
       </c>
       <c r="B50" t="n">
-        <v>97983</v>
+        <v>99035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6261,21 +6271,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6293,10 +6303,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518477</v>
+        <v>518426</v>
       </c>
       <c r="R50" t="n">
-        <v>6534997</v>
+        <v>6534993</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6355,16 +6365,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120490271</t>
+          <t>https://artportalen.se/Sighting/120490371</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133676469</v>
+        <v>120490271</v>
       </c>
       <c r="B51" t="n">
-        <v>58061</v>
+        <v>97983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6372,53 +6382,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102626</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Törnskata</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lanius collurio</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hjärta, Nrk</t>
+          <t>Molångsfallet, Nrk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>516431</v>
+        <v>518477</v>
       </c>
       <c r="R51" t="n">
-        <v>6534878</v>
+        <v>6534997</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6442,22 +6444,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:25</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6466,55 +6458,56 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Patrick Fritzson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133676469</t>
+          <t>https://artportalen.se/Sighting/120490271</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134223604</v>
+        <v>133676469</v>
       </c>
       <c r="B52" t="n">
-        <v>57386</v>
+        <v>58061</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102954</v>
+        <v>102626</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -6523,7 +6516,11 @@
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>spel/sång</t>
@@ -6566,22 +6563,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6607,33 +6604,33 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134223604</t>
+          <t>https://artportalen.se/Sighting/133676469</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134174906</v>
+        <v>134223604</v>
       </c>
       <c r="B53" t="n">
-        <v>58658</v>
+        <v>57386</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103044</v>
+        <v>102954</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6690,22 +6687,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6731,55 +6728,63 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134174906</t>
+          <t>https://artportalen.se/Sighting/134223604</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>62686291</v>
+        <v>134174906</v>
       </c>
       <c r="B54" t="n">
-        <v>107708</v>
+        <v>58658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>245</v>
+        <v>103044</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Skogsklocka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Campanula cervicaria</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ö:a Hjärta 6450/1750, Nrk</t>
+          <t>Hjärta, Nrk</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>518089</v>
+        <v>516431</v>
       </c>
       <c r="R54" t="n">
-        <v>6534405</v>
+        <v>6534878</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6806,17 +6811,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>1980-07-10</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>1980-07-10</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>9 ex. 2016 ej återfunnen. Biotopen oigenkännlig</t>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6827,74 +6837,73 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Ej återfunnen 2016. Biotopen sannolikt alltför förändrad</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Patrick Fritzson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62686291</t>
+          <t>https://artportalen.se/Sighting/134174906</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>85451223</v>
+        <v>62686291</v>
       </c>
       <c r="B55" t="n">
-        <v>80367</v>
+        <v>107708</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6457</v>
+        <v>245</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>väst Hjärtaviken, Nrk</t>
+          <t>Ö:a Hjärta 6450/1750, Nrk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>517772</v>
+        <v>518089</v>
       </c>
       <c r="R55" t="n">
-        <v>6533805</v>
+        <v>6534405</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6918,12 +6927,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>1980-07-10</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>1980-07-10</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>9 ex. 2016 ej återfunnen. Biotopen oigenkännlig</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6934,31 +6948,36 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Ej återfunnen 2016. Biotopen sannolikt alltför förändrad</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451223</t>
+          <t>https://artportalen.se/Sighting/62686291</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>78430052</v>
+        <v>85451223</v>
       </c>
       <c r="B56" t="n">
-        <v>96348</v>
+        <v>80367</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6966,37 +6985,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2810</v>
+        <v>6457</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Charlottendal, Nrk</t>
+          <t>väst Hjärtaviken, Nrk</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>518424</v>
+        <v>517772</v>
       </c>
       <c r="R56" t="n">
-        <v>6533707</v>
+        <v>6533805</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7020,12 +7039,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2019-06-15</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2019-06-15</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7040,27 +7059,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78430052</t>
+          <t>https://artportalen.se/Sighting/85451223</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>54014137</v>
+        <v>78430052</v>
       </c>
       <c r="B57" t="n">
-        <v>91872</v>
+        <v>96348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7068,34 +7087,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>2810</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>Charlottendal, Nrk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518326</v>
+        <v>518424</v>
       </c>
       <c r="R57" t="n">
-        <v>6533577</v>
+        <v>6533707</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7122,12 +7141,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-06-15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-06-15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7142,65 +7161,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54014137</t>
+          <t>https://artportalen.se/Sighting/78430052</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>85451486</v>
+        <v>54014137</v>
       </c>
       <c r="B58" t="n">
-        <v>92205</v>
+        <v>91872</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>73</v>
+        <v>5447</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fomitopsis pulvinascens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Pilát) Niemelä &amp; Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Baggesand, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518702</v>
+        <v>518326</v>
       </c>
       <c r="R58" t="n">
-        <v>6533363</v>
+        <v>6533577</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7224,12 +7243,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7244,27 +7263,27 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451486</t>
+          <t>https://artportalen.se/Sighting/54014137</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>80563834</v>
+        <v>85451486</v>
       </c>
       <c r="B59" t="n">
-        <v>91909</v>
+        <v>92205</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7272,37 +7291,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>73</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>518862</v>
+        <v>518702</v>
       </c>
       <c r="R59" t="n">
-        <v>6532925</v>
+        <v>6533363</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7326,12 +7345,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7342,33 +7361,28 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>låga av gran</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563834</t>
+          <t>https://artportalen.se/Sighting/85451486</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>85451487</v>
+        <v>80563834</v>
       </c>
       <c r="B60" t="n">
         <v>91909</v>
@@ -7399,17 +7413,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Baggesand, Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518897</v>
+        <v>518862</v>
       </c>
       <c r="R60" t="n">
-        <v>6532914</v>
+        <v>6532925</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7433,12 +7447,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7449,28 +7463,33 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>låga av gran</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451487</t>
+          <t>https://artportalen.se/Sighting/80563834</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>85451488</v>
+        <v>85451487</v>
       </c>
       <c r="B61" t="n">
         <v>91909</v>
@@ -7505,10 +7524,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518856</v>
+        <v>518897</v>
       </c>
       <c r="R61" t="n">
-        <v>6532925</v>
+        <v>6532914</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7566,57 +7585,51 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451488</t>
+          <t>https://artportalen.se/Sighting/85451487</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>55322405</v>
+        <v>85451488</v>
       </c>
       <c r="B62" t="n">
-        <v>91966</v>
+        <v>91909</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5321</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518957</v>
+        <v>518856</v>
       </c>
       <c r="R62" t="n">
-        <v>6533260</v>
+        <v>6532925</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7643,12 +7656,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7657,31 +7670,30 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322405</t>
+          <t>https://artportalen.se/Sighting/85451488</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>98101330</v>
+        <v>55322405</v>
       </c>
       <c r="B63" t="n">
         <v>91966</v>
@@ -7709,27 +7721,26 @@
           <t>(Fr.) Ryvarden</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>N Baggesandstjärnen, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518968</v>
+        <v>518957</v>
       </c>
       <c r="R63" t="n">
-        <v>6533243</v>
+        <v>6533260</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7753,22 +7764,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2014-09-14</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7784,27 +7785,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98101330</t>
+          <t>https://artportalen.se/Sighting/55322405</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>85451507</v>
+        <v>98101330</v>
       </c>
       <c r="B64" t="n">
-        <v>79707</v>
+        <v>91966</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7812,37 +7813,44 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6431</v>
+        <v>5321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Baggesand, Nrk</t>
+          <t>N Baggesandstjärnen, Nrk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518735</v>
+        <v>518968</v>
       </c>
       <c r="R64" t="n">
-        <v>6533098</v>
+        <v>6533243</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7866,12 +7874,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2022-01-13</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2022-01-13</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7880,55 +7898,56 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451507</t>
+          <t>https://artportalen.se/Sighting/98101330</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>85451509</v>
+        <v>85451507</v>
       </c>
       <c r="B65" t="n">
-        <v>79084</v>
+        <v>79707</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6431</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7938,10 +7957,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518825</v>
+        <v>518735</v>
       </c>
       <c r="R65" t="n">
-        <v>6533312</v>
+        <v>6533098</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7999,16 +8018,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451509</t>
+          <t>https://artportalen.se/Sighting/85451507</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>85451483</v>
+        <v>85451509</v>
       </c>
       <c r="B66" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8016,21 +8035,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8040,10 +8059,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518829</v>
+        <v>518825</v>
       </c>
       <c r="R66" t="n">
-        <v>6533317</v>
+        <v>6533312</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8101,38 +8120,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451483</t>
+          <t>https://artportalen.se/Sighting/85451509</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>85451531</v>
+        <v>85451483</v>
       </c>
       <c r="B67" t="n">
-        <v>80367</v>
+        <v>79946</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6457</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8142,10 +8161,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518726</v>
+        <v>518829</v>
       </c>
       <c r="R67" t="n">
-        <v>6533324</v>
+        <v>6533317</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8203,13 +8222,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451531</t>
+          <t>https://artportalen.se/Sighting/85451483</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>85451532</v>
+        <v>85451531</v>
       </c>
       <c r="B68" t="n">
         <v>80367</v>
@@ -8244,10 +8263,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518706</v>
+        <v>518726</v>
       </c>
       <c r="R68" t="n">
-        <v>6533361</v>
+        <v>6533324</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8305,16 +8324,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451532</t>
+          <t>https://artportalen.se/Sighting/85451531</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119730876</v>
+        <v>85451532</v>
       </c>
       <c r="B69" t="n">
-        <v>57899</v>
+        <v>80367</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8322,45 +8341,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100067</v>
+        <v>6457</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Wallr.) Otálora et al.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518873</v>
+        <v>518706</v>
       </c>
       <c r="R69" t="n">
-        <v>6533167</v>
+        <v>6533361</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8384,12 +8395,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8404,27 +8415,27 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119730876</t>
+          <t>https://artportalen.se/Sighting/85451532</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>80563835</v>
+        <v>119730876</v>
       </c>
       <c r="B70" t="n">
-        <v>5179</v>
+        <v>57899</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8432,37 +8443,45 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100526</v>
+        <v>100067</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Baggesand, Nrk</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518851</v>
+        <v>518873</v>
       </c>
       <c r="R70" t="n">
-        <v>6532925</v>
+        <v>6533167</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8486,12 +8505,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2024-09-12</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8502,83 +8521,66 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563835</t>
+          <t>https://artportalen.se/Sighting/119730876</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>79351146</v>
+        <v>80563835</v>
       </c>
       <c r="B71" t="n">
-        <v>58497</v>
+        <v>5179</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102990</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Baggesandtärnen, väster om., Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518745</v>
+        <v>518851</v>
       </c>
       <c r="R71" t="n">
-        <v>6533090</v>
+        <v>6532925</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8605,22 +8607,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2019-04-25</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>18:00</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2019-04-25</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>20:00</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8631,48 +8623,53 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79351146</t>
+          <t>https://artportalen.se/Sighting/80563835</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>79351057</v>
+        <v>79351146</v>
       </c>
       <c r="B72" t="n">
-        <v>58327</v>
+        <v>58497</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>102990</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8695,14 +8692,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Baggesandtärnen, Nrk</t>
+          <t>Baggesandtärnen, väster om., Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518755</v>
+        <v>518745</v>
       </c>
       <c r="R72" t="n">
-        <v>6532980</v>
+        <v>6533090</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8770,38 +8767,38 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79351057</t>
+          <t>https://artportalen.se/Sighting/79351146</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>90856737</v>
+        <v>79351057</v>
       </c>
       <c r="B73" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -8813,23 +8810,23 @@
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Baggesand Ö om, Nrk</t>
+          <t>Baggesandtärnen, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>518881</v>
+        <v>518755</v>
       </c>
       <c r="R73" t="n">
-        <v>6533297</v>
+        <v>6532980</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8853,12 +8850,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-02-12</t>
+          <t>2019-04-25</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-02-12</t>
+          <t>2019-04-25</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8873,49 +8880,49 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90856737</t>
+          <t>https://artportalen.se/Sighting/79351057</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>55322391</v>
+        <v>90856737</v>
       </c>
       <c r="B74" t="n">
-        <v>101326</v>
+        <v>58114</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -8923,22 +8930,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Baggesand Ö om, Nrk</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518981</v>
+        <v>518881</v>
       </c>
       <c r="R74" t="n">
-        <v>6533359</v>
+        <v>6533297</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8962,12 +8974,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2021-02-12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2014-09-14</t>
+          <t>2021-02-12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8982,16 +8994,125 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90856737</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>55322391</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>518981</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6533359</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2014-09-14</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Viktor Säfve</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Viktor Säfve</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/55322391</t>
         </is>
@@ -9072,6 +9193,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -2643,7 +2643,7 @@
         <v>135859839</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -2643,7 +2643,7 @@
         <v>135859839</v>
       </c>
       <c r="B19" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -2643,7 +2643,7 @@
         <v>135859839</v>
       </c>
       <c r="B19" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -2643,7 +2643,7 @@
         <v>135859839</v>
       </c>
       <c r="B19" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -2643,7 +2643,7 @@
         <v>135859839</v>
       </c>
       <c r="B19" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/S 676-2025 artfynd.xlsx
+++ b/artfynd/S 676-2025 artfynd.xlsx
@@ -2643,7 +2643,7 @@
         <v>135859839</v>
       </c>
       <c r="B19" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
